--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129761739</v>
+        <v>129761765</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -716,7 +716,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535518</v>
+        <v>535524</v>
       </c>
       <c r="R2" t="n">
-        <v>6845875</v>
+        <v>6845867</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet.</t>
+          <t>Har lavskrikan på film. ska länka när jag fått upp filmen på internet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,37 +803,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129761765</v>
+        <v>129761686</v>
       </c>
       <c r="B3" t="n">
-        <v>57839</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535524</v>
+        <v>535552</v>
       </c>
       <c r="R3" t="n">
-        <v>6845867</v>
+        <v>6846061</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,12 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Har lavskrikan på film. ska länka när jag fått upp filmen på internet.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129761686</v>
+        <v>129764334</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>91886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,39 +937,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535552</v>
+        <v>535492</v>
       </c>
       <c r="R4" t="n">
-        <v>6846061</v>
+        <v>6846029</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,27 +997,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1051,6 +1024,3473 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129764173</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78833</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>535509</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6845947</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129764349</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>535598</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6846065</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129764337</v>
+      </c>
+      <c r="B7" t="n">
+        <v>75188</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>535577</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6846056</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129764363</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92041</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>535632</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6846079</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129764308</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91609</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>535447</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6845978</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129764256</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98769</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>535430</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6845927</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129764213</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98769</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>535466</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6845930</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129764154</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79076</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>535592</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6845934</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129764182</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>535475</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6845922</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129764285</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>535385</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6845929</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129764358</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>535632</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6846079</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129764380</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98769</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>535651</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6846125</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129764178</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98769</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>535471</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6845973</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129764210</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79076</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>535529</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6845938</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129764208</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>535515</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6845927</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129764305</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98769</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>535439</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6845968</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129764166</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91886</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535555</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6845967</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129764331</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>535494</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6846030</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129764187</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97015</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>53</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>535460</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6845848</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129764223</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>535470</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6845918</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129764255</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>535439</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6845944</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129764320</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91886</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>658</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>535446</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6846015</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129761739</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>535518</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6845875</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129764260</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98769</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>535417</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6845933</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129764299</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78833</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>535408</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6845995</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129764374</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>535655</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6846098</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129764343</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91886</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>658</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>535587</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6846066</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129764312</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91886</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>658</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>535470</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6845980</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129764159</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>535563</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6845935</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129764388</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97015</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>53</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>535670</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6846121</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129764168</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91588</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>535523</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6845943</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129764275</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98769</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>535415</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6845934</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129764302</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98769</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gråkölen, Hls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>535410</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6845976</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129761765</v>
+        <v>129761686</v>
       </c>
       <c r="B2" t="n">
-        <v>57840</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535524</v>
+        <v>535552</v>
       </c>
       <c r="R2" t="n">
-        <v>6845867</v>
+        <v>6846061</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Har lavskrikan på film. ska länka när jag fått upp filmen på internet.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129761686</v>
+        <v>129764334</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>91886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,39 +809,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -854,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535552</v>
+        <v>535492</v>
       </c>
       <c r="R3" t="n">
-        <v>6846061</v>
+        <v>6846029</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,27 +869,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -926,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764334</v>
+        <v>129764173</v>
       </c>
       <c r="B4" t="n">
-        <v>91886</v>
+        <v>78833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535492</v>
+        <v>535509</v>
       </c>
       <c r="R4" t="n">
-        <v>6846029</v>
+        <v>6845947</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764173</v>
+        <v>129764349</v>
       </c>
       <c r="B5" t="n">
-        <v>78833</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535509</v>
+        <v>535598</v>
       </c>
       <c r="R5" t="n">
-        <v>6845947</v>
+        <v>6846065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764349</v>
+        <v>129764337</v>
       </c>
       <c r="B6" t="n">
-        <v>91588</v>
+        <v>75188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535598</v>
+        <v>535577</v>
       </c>
       <c r="R6" t="n">
-        <v>6846065</v>
+        <v>6846056</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764337</v>
+        <v>129764363</v>
       </c>
       <c r="B7" t="n">
-        <v>75188</v>
+        <v>92041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535577</v>
+        <v>535632</v>
       </c>
       <c r="R7" t="n">
-        <v>6846056</v>
+        <v>6846079</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,32 +1303,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129764363</v>
+        <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>92041</v>
+        <v>91609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535632</v>
+        <v>535447</v>
       </c>
       <c r="R8" t="n">
-        <v>6846079</v>
+        <v>6845978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,37 +1404,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764308</v>
+        <v>129764256</v>
       </c>
       <c r="B9" t="n">
-        <v>91609</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1469,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535447</v>
+        <v>535430</v>
       </c>
       <c r="R9" t="n">
-        <v>6845978</v>
+        <v>6845927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764256</v>
+        <v>129764213</v>
       </c>
       <c r="B10" t="n">
         <v>98769</v>
@@ -1562,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1579,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535430</v>
+        <v>535466</v>
       </c>
       <c r="R10" t="n">
-        <v>6845927</v>
+        <v>6845930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,46 +1624,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129764213</v>
+        <v>129764154</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1689,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535466</v>
+        <v>535592</v>
       </c>
       <c r="R11" t="n">
-        <v>6845930</v>
+        <v>6845934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129764154</v>
+        <v>129764182</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>91588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535592</v>
+        <v>535475</v>
       </c>
       <c r="R12" t="n">
-        <v>6845934</v>
+        <v>6845922</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,37 +1826,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129764182</v>
+        <v>129764285</v>
       </c>
       <c r="B13" t="n">
-        <v>91588</v>
+        <v>8439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1891,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535475</v>
+        <v>535385</v>
       </c>
       <c r="R13" t="n">
-        <v>6845922</v>
+        <v>6845929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,43 +1933,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129764285</v>
+        <v>129764358</v>
       </c>
       <c r="B14" t="n">
-        <v>8439</v>
+        <v>91588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1998,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535385</v>
+        <v>535632</v>
       </c>
       <c r="R14" t="n">
-        <v>6845929</v>
+        <v>6846079</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,37 +2034,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129764358</v>
+        <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>91588</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2099,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535632</v>
+        <v>535651</v>
       </c>
       <c r="R15" t="n">
-        <v>6846079</v>
+        <v>6846125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2144,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129764380</v>
+        <v>129764178</v>
       </c>
       <c r="B16" t="n">
         <v>98769</v>
@@ -2192,7 +2174,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2209,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535651</v>
+        <v>535471</v>
       </c>
       <c r="R16" t="n">
-        <v>6846125</v>
+        <v>6845973</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,46 +2254,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764178</v>
+        <v>129764208</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2319,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535471</v>
+        <v>535515</v>
       </c>
       <c r="R17" t="n">
-        <v>6845973</v>
+        <v>6845927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,13 +2335,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2483,42 +2465,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129764208</v>
+        <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2526,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535515</v>
+        <v>535439</v>
       </c>
       <c r="R19" t="n">
-        <v>6845927</v>
+        <v>6845968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,17 +2550,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2593,46 +2575,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129764305</v>
+        <v>129764166</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>91886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2640,10 +2613,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535439</v>
+        <v>535555</v>
       </c>
       <c r="R20" t="n">
-        <v>6845968</v>
+        <v>6845967</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764166</v>
+        <v>129764331</v>
       </c>
       <c r="B21" t="n">
-        <v>91886</v>
+        <v>91588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,21 +2687,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535555</v>
+        <v>535494</v>
       </c>
       <c r="R21" t="n">
-        <v>6845967</v>
+        <v>6846030</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764331</v>
+        <v>129764187</v>
       </c>
       <c r="B22" t="n">
-        <v>91588</v>
+        <v>97015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,26 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2842,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535494</v>
+        <v>535460</v>
       </c>
       <c r="R22" t="n">
-        <v>6846030</v>
+        <v>6845848</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,10 +2879,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129764187</v>
+        <v>129764223</v>
       </c>
       <c r="B23" t="n">
-        <v>97015</v>
+        <v>91588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,27 +2890,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2944,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535460</v>
+        <v>535470</v>
       </c>
       <c r="R23" t="n">
-        <v>6845848</v>
+        <v>6845918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764223</v>
+        <v>129764255</v>
       </c>
       <c r="B24" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,26 +2991,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3045,10 +3023,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535470</v>
+        <v>535439</v>
       </c>
       <c r="R24" t="n">
-        <v>6845918</v>
+        <v>6845944</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,13 +3061,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3108,7 +3090,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129764255</v>
+        <v>129761739</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3136,12 +3118,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3151,13 +3141,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535439</v>
+        <v>535518</v>
       </c>
       <c r="R25" t="n">
-        <v>6845944</v>
+        <v>6845875</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3184,14 +3174,24 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3319,50 +3319,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129761739</v>
+        <v>129764260</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3370,13 +3366,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535518</v>
+        <v>535417</v>
       </c>
       <c r="R27" t="n">
-        <v>6845875</v>
+        <v>6845933</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3403,32 +3399,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3447,46 +3429,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764260</v>
+        <v>129764299</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>78833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3494,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535417</v>
+        <v>535408</v>
       </c>
       <c r="R28" t="n">
-        <v>6845933</v>
+        <v>6845995</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764299</v>
+        <v>129764374</v>
       </c>
       <c r="B29" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3568,26 +3541,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3595,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535408</v>
+        <v>535655</v>
       </c>
       <c r="R29" t="n">
-        <v>6845995</v>
+        <v>6846098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,13 +3611,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3658,10 +3640,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,31 +3651,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3701,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R30" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3739,17 +3716,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3768,7 +3741,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129764343</v>
+        <v>129764312</v>
       </c>
       <c r="B31" t="n">
         <v>91886</v>
@@ -3806,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535587</v>
+        <v>535470</v>
       </c>
       <c r="R31" t="n">
-        <v>6846066</v>
+        <v>6845980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129764312</v>
+        <v>129764159</v>
       </c>
       <c r="B32" t="n">
-        <v>91886</v>
+        <v>91588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3880,21 +3853,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535470</v>
+        <v>535563</v>
       </c>
       <c r="R32" t="n">
-        <v>6845980</v>
+        <v>6845935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3970,10 +3943,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764159</v>
+        <v>129764388</v>
       </c>
       <c r="B33" t="n">
-        <v>91588</v>
+        <v>97015</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,26 +3954,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4008,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535563</v>
+        <v>535670</v>
       </c>
       <c r="R33" t="n">
-        <v>6845935</v>
+        <v>6846121</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,10 +4045,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764388</v>
+        <v>129764168</v>
       </c>
       <c r="B34" t="n">
-        <v>97015</v>
+        <v>91588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4082,27 +4056,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4110,10 +4083,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535670</v>
+        <v>535523</v>
       </c>
       <c r="R34" t="n">
-        <v>6846121</v>
+        <v>6845943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,37 +4146,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764168</v>
+        <v>129764275</v>
       </c>
       <c r="B35" t="n">
-        <v>91588</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4211,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535523</v>
+        <v>535415</v>
       </c>
       <c r="R35" t="n">
-        <v>6845943</v>
+        <v>6845934</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4274,7 +4256,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129764275</v>
+        <v>129764302</v>
       </c>
       <c r="B36" t="n">
         <v>98769</v>
@@ -4304,7 +4286,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4321,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535415</v>
+        <v>535410</v>
       </c>
       <c r="R36" t="n">
-        <v>6845934</v>
+        <v>6845976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4384,46 +4366,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129764302</v>
+        <v>129761765</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>57840</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4431,13 +4417,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535410</v>
+        <v>535524</v>
       </c>
       <c r="R37" t="n">
-        <v>6845976</v>
+        <v>6845867</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4464,18 +4450,32 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Har lavskrikan på film. ska länka när jag fått upp filmen på internet. https://youtu.be/GXFxs2jfycE</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>129764334</v>
       </c>
       <c r="B3" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764173</v>
+        <v>129764349</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535509</v>
+        <v>535598</v>
       </c>
       <c r="R4" t="n">
-        <v>6845947</v>
+        <v>6846065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764349</v>
+        <v>129764363</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535598</v>
+        <v>535632</v>
       </c>
       <c r="R5" t="n">
-        <v>6846065</v>
+        <v>6846079</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
         <v>129764337</v>
       </c>
       <c r="B6" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764363</v>
+        <v>129764173</v>
       </c>
       <c r="B7" t="n">
-        <v>92041</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535632</v>
+        <v>535509</v>
       </c>
       <c r="R7" t="n">
-        <v>6846079</v>
+        <v>6845947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129764256</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>129764213</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>129764154</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129764182</v>
       </c>
       <c r="B12" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>129764358</v>
       </c>
       <c r="B14" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129764178</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764208</v>
+        <v>129764210</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,31 +2265,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535515</v>
+        <v>535529</v>
       </c>
       <c r="R17" t="n">
-        <v>6845927</v>
+        <v>6845938</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,17 +2330,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129764210</v>
+        <v>129764208</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,26 +2366,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2402,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535529</v>
+        <v>535515</v>
       </c>
       <c r="R18" t="n">
-        <v>6845938</v>
+        <v>6845927</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,13 +2436,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129764166</v>
       </c>
       <c r="B20" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764331</v>
+        <v>129764187</v>
       </c>
       <c r="B21" t="n">
-        <v>91588</v>
+        <v>97020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,26 +2687,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2714,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535494</v>
+        <v>535460</v>
       </c>
       <c r="R21" t="n">
-        <v>6846030</v>
+        <v>6845848</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,10 +2778,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764187</v>
+        <v>129764331</v>
       </c>
       <c r="B22" t="n">
-        <v>97015</v>
+        <v>91593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,27 +2789,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535460</v>
+        <v>535494</v>
       </c>
       <c r="R22" t="n">
-        <v>6845848</v>
+        <v>6846030</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
         <v>129764223</v>
       </c>
       <c r="B23" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129764320</v>
       </c>
       <c r="B26" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,46 +3319,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129764260</v>
+        <v>129764299</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>78838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3366,10 +3357,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535417</v>
+        <v>535408</v>
       </c>
       <c r="R27" t="n">
-        <v>6845933</v>
+        <v>6845995</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,37 +3420,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764299</v>
+        <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>78833</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535408</v>
+        <v>535417</v>
       </c>
       <c r="R28" t="n">
-        <v>6845995</v>
+        <v>6845933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,31 +3541,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3573,10 +3568,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R29" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,17 +3606,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3640,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B30" t="n">
-        <v>91886</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3651,26 +3642,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3678,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R30" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,13 +3712,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>129764312</v>
       </c>
       <c r="B31" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>129764159</v>
       </c>
       <c r="B32" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>129764388</v>
       </c>
       <c r="B33" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>129764168</v>
       </c>
       <c r="B34" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>129764275</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>129764302</v>
       </c>
       <c r="B36" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764349</v>
+        <v>129764363</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535598</v>
+        <v>535632</v>
       </c>
       <c r="R4" t="n">
-        <v>6846065</v>
+        <v>6846079</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764363</v>
+        <v>129764349</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535632</v>
+        <v>535598</v>
       </c>
       <c r="R5" t="n">
-        <v>6846079</v>
+        <v>6846065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764210</v>
+        <v>129764208</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,26 +2265,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2292,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535529</v>
+        <v>535515</v>
       </c>
       <c r="R17" t="n">
-        <v>6845938</v>
+        <v>6845927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,13 +2335,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2355,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129764208</v>
+        <v>129764210</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,31 +2375,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2398,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535515</v>
+        <v>535529</v>
       </c>
       <c r="R18" t="n">
-        <v>6845927</v>
+        <v>6845938</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,17 +2440,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764187</v>
+        <v>129764331</v>
       </c>
       <c r="B21" t="n">
-        <v>97020</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,27 +2687,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2715,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535460</v>
+        <v>535494</v>
       </c>
       <c r="R21" t="n">
-        <v>6845848</v>
+        <v>6846030</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764331</v>
+        <v>129764187</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
+        <v>97020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,26 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535494</v>
+        <v>535460</v>
       </c>
       <c r="R22" t="n">
-        <v>6846030</v>
+        <v>6845848</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764255</v>
+        <v>129764320</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,31 +2991,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3023,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535439</v>
+        <v>535446</v>
       </c>
       <c r="R24" t="n">
-        <v>6845944</v>
+        <v>6846015</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,17 +3056,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3090,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129761739</v>
+        <v>129764255</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3118,20 +3109,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3141,13 +3124,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535518</v>
+        <v>535439</v>
       </c>
       <c r="R25" t="n">
-        <v>6845875</v>
+        <v>6845944</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3174,24 +3157,14 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129764320</v>
+        <v>129761739</v>
       </c>
       <c r="B26" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,26 +3202,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3256,13 +3242,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535446</v>
+        <v>535518</v>
       </c>
       <c r="R26" t="n">
-        <v>6846015</v>
+        <v>6845875</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3289,18 +3275,32 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B29" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,26 +3541,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3568,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R29" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,13 +3611,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3631,10 +3640,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3642,31 +3651,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R30" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,17 +3716,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129764312</v>
+        <v>129764159</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535470</v>
+        <v>535563</v>
       </c>
       <c r="R31" t="n">
-        <v>6845980</v>
+        <v>6845935</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129764159</v>
+        <v>129764312</v>
       </c>
       <c r="B32" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535563</v>
+        <v>535470</v>
       </c>
       <c r="R32" t="n">
-        <v>6845935</v>
+        <v>6845980</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,36 +3943,44 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764388</v>
+        <v>129764275</v>
       </c>
       <c r="B33" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -3982,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535670</v>
+        <v>535415</v>
       </c>
       <c r="R33" t="n">
-        <v>6846121</v>
+        <v>6845934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,37 +4053,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764168</v>
+        <v>129764302</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4083,10 +4100,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535523</v>
+        <v>535410</v>
       </c>
       <c r="R34" t="n">
-        <v>6845943</v>
+        <v>6845976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,44 +4163,36 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764275</v>
+        <v>129764388</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>97020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4193,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535415</v>
+        <v>535670</v>
       </c>
       <c r="R35" t="n">
-        <v>6845934</v>
+        <v>6846121</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,46 +4265,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129764302</v>
+        <v>129764168</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535410</v>
+        <v>535523</v>
       </c>
       <c r="R36" t="n">
-        <v>6845976</v>
+        <v>6845943</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764363</v>
+        <v>129764173</v>
       </c>
       <c r="B4" t="n">
-        <v>92046</v>
+        <v>78838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535632</v>
+        <v>535509</v>
       </c>
       <c r="R4" t="n">
-        <v>6846079</v>
+        <v>6845947</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1101,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764337</v>
+        <v>129764363</v>
       </c>
       <c r="B6" t="n">
-        <v>75193</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535577</v>
+        <v>535632</v>
       </c>
       <c r="R6" t="n">
-        <v>6846056</v>
+        <v>6846079</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764173</v>
+        <v>129764337</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>75193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535509</v>
+        <v>535577</v>
       </c>
       <c r="R7" t="n">
-        <v>6845947</v>
+        <v>6846056</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764256</v>
+        <v>129764213</v>
       </c>
       <c r="B9" t="n">
         <v>98774</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535430</v>
+        <v>535466</v>
       </c>
       <c r="R9" t="n">
-        <v>6845927</v>
+        <v>6845930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764213</v>
+        <v>129764256</v>
       </c>
       <c r="B10" t="n">
         <v>98774</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535466</v>
+        <v>535430</v>
       </c>
       <c r="R10" t="n">
-        <v>6845930</v>
+        <v>6845927</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129764380</v>
+        <v>129764178</v>
       </c>
       <c r="B15" t="n">
         <v>98774</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535651</v>
+        <v>535471</v>
       </c>
       <c r="R15" t="n">
-        <v>6846125</v>
+        <v>6845973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129764178</v>
+        <v>129764380</v>
       </c>
       <c r="B16" t="n">
         <v>98774</v>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535471</v>
+        <v>535651</v>
       </c>
       <c r="R16" t="n">
-        <v>6845973</v>
+        <v>6846125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764208</v>
+        <v>129764210</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,31 +2265,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535515</v>
+        <v>535529</v>
       </c>
       <c r="R17" t="n">
-        <v>6845927</v>
+        <v>6845938</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,17 +2330,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129764210</v>
+        <v>129764208</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,26 +2366,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2402,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535529</v>
+        <v>535515</v>
       </c>
       <c r="R18" t="n">
-        <v>6845938</v>
+        <v>6845927</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,13 +2436,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764331</v>
+        <v>129764187</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>97020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,26 +2687,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2714,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535494</v>
+        <v>535460</v>
       </c>
       <c r="R21" t="n">
-        <v>6846030</v>
+        <v>6845848</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,10 +2778,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764187</v>
+        <v>129764331</v>
       </c>
       <c r="B22" t="n">
-        <v>97020</v>
+        <v>91593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,27 +2789,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535460</v>
+        <v>535494</v>
       </c>
       <c r="R22" t="n">
-        <v>6845848</v>
+        <v>6846030</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3319,37 +3319,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129764299</v>
+        <v>129764260</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3357,10 +3366,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535408</v>
+        <v>535417</v>
       </c>
       <c r="R27" t="n">
-        <v>6845995</v>
+        <v>6845933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,46 +3429,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764260</v>
+        <v>129764299</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>78838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535417</v>
+        <v>535408</v>
       </c>
       <c r="R28" t="n">
-        <v>6845933</v>
+        <v>6845995</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,31 +3541,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3573,10 +3568,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R29" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,17 +3606,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3640,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3651,26 +3642,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3678,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R30" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,13 +3712,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129764159</v>
+        <v>129764312</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535563</v>
+        <v>535470</v>
       </c>
       <c r="R31" t="n">
-        <v>6845935</v>
+        <v>6845980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129764312</v>
+        <v>129764159</v>
       </c>
       <c r="B32" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535470</v>
+        <v>535563</v>
       </c>
       <c r="R32" t="n">
-        <v>6845980</v>
+        <v>6845935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,46 +3943,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764275</v>
+        <v>129764168</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3990,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535415</v>
+        <v>535523</v>
       </c>
       <c r="R33" t="n">
-        <v>6845934</v>
+        <v>6845943</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4053,7 +4044,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764302</v>
+        <v>129764275</v>
       </c>
       <c r="B34" t="n">
         <v>98774</v>
@@ -4083,7 +4074,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4100,10 +4091,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535410</v>
+        <v>535415</v>
       </c>
       <c r="R34" t="n">
-        <v>6845976</v>
+        <v>6845934</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4163,36 +4154,44 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764388</v>
+        <v>129764302</v>
       </c>
       <c r="B35" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4202,10 +4201,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535670</v>
+        <v>535410</v>
       </c>
       <c r="R35" t="n">
-        <v>6846121</v>
+        <v>6845976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4265,10 +4264,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129764168</v>
+        <v>129764388</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>97020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4276,26 +4275,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535523</v>
+        <v>535670</v>
       </c>
       <c r="R36" t="n">
-        <v>6845943</v>
+        <v>6846121</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764173</v>
+        <v>129764337</v>
       </c>
       <c r="B4" t="n">
-        <v>78838</v>
+        <v>75193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535509</v>
+        <v>535577</v>
       </c>
       <c r="R4" t="n">
-        <v>6845947</v>
+        <v>6846056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764349</v>
+        <v>129764173</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>78838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535598</v>
+        <v>535509</v>
       </c>
       <c r="R5" t="n">
-        <v>6846065</v>
+        <v>6845947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764363</v>
+        <v>129764349</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535632</v>
+        <v>535598</v>
       </c>
       <c r="R6" t="n">
-        <v>6846079</v>
+        <v>6846065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764337</v>
+        <v>129764363</v>
       </c>
       <c r="B7" t="n">
-        <v>75193</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535577</v>
+        <v>535632</v>
       </c>
       <c r="R7" t="n">
-        <v>6846056</v>
+        <v>6846079</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764213</v>
+        <v>129764256</v>
       </c>
       <c r="B9" t="n">
         <v>98774</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535466</v>
+        <v>535430</v>
       </c>
       <c r="R9" t="n">
-        <v>6845930</v>
+        <v>6845927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764256</v>
+        <v>129764213</v>
       </c>
       <c r="B10" t="n">
         <v>98774</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535430</v>
+        <v>535466</v>
       </c>
       <c r="R10" t="n">
-        <v>6845927</v>
+        <v>6845930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129764178</v>
+        <v>129764380</v>
       </c>
       <c r="B15" t="n">
         <v>98774</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535471</v>
+        <v>535651</v>
       </c>
       <c r="R15" t="n">
-        <v>6845973</v>
+        <v>6846125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129764380</v>
+        <v>129764178</v>
       </c>
       <c r="B16" t="n">
         <v>98774</v>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535651</v>
+        <v>535471</v>
       </c>
       <c r="R16" t="n">
-        <v>6846125</v>
+        <v>6845973</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764210</v>
+        <v>129764208</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,26 +2265,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2292,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535529</v>
+        <v>535515</v>
       </c>
       <c r="R17" t="n">
-        <v>6845938</v>
+        <v>6845927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,13 +2335,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2355,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129764208</v>
+        <v>129764210</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,31 +2375,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2398,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535515</v>
+        <v>535529</v>
       </c>
       <c r="R18" t="n">
-        <v>6845927</v>
+        <v>6845938</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,17 +2440,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3319,46 +3319,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129764260</v>
+        <v>129764299</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>78838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3366,10 +3357,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535417</v>
+        <v>535408</v>
       </c>
       <c r="R27" t="n">
-        <v>6845933</v>
+        <v>6845995</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,37 +3420,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764299</v>
+        <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>78838</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535408</v>
+        <v>535417</v>
       </c>
       <c r="R28" t="n">
-        <v>6845995</v>
+        <v>6845933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129764312</v>
+        <v>129764159</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535470</v>
+        <v>535563</v>
       </c>
       <c r="R31" t="n">
-        <v>6845980</v>
+        <v>6845935</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129764159</v>
+        <v>129764312</v>
       </c>
       <c r="B32" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535563</v>
+        <v>535470</v>
       </c>
       <c r="R32" t="n">
-        <v>6845935</v>
+        <v>6845980</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,10 +3943,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764168</v>
+        <v>129764388</v>
       </c>
       <c r="B33" t="n">
-        <v>91593</v>
+        <v>97020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,26 +3954,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3981,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535523</v>
+        <v>535670</v>
       </c>
       <c r="R33" t="n">
-        <v>6845943</v>
+        <v>6846121</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,46 +4045,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764275</v>
+        <v>129764168</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4091,10 +4083,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535415</v>
+        <v>535523</v>
       </c>
       <c r="R34" t="n">
-        <v>6845934</v>
+        <v>6845943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,7 +4146,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764302</v>
+        <v>129764275</v>
       </c>
       <c r="B35" t="n">
         <v>98774</v>
@@ -4184,7 +4176,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4201,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535410</v>
+        <v>535415</v>
       </c>
       <c r="R35" t="n">
-        <v>6845976</v>
+        <v>6845934</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4264,36 +4256,44 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129764388</v>
+        <v>129764302</v>
       </c>
       <c r="B36" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535670</v>
+        <v>535410</v>
       </c>
       <c r="R36" t="n">
-        <v>6846121</v>
+        <v>6845976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>129764334</v>
       </c>
       <c r="B3" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764337</v>
+        <v>129764349</v>
       </c>
       <c r="B4" t="n">
-        <v>75193</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535577</v>
+        <v>535598</v>
       </c>
       <c r="R4" t="n">
-        <v>6846056</v>
+        <v>6846065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764173</v>
+        <v>129764363</v>
       </c>
       <c r="B5" t="n">
-        <v>78838</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535509</v>
+        <v>535632</v>
       </c>
       <c r="R5" t="n">
-        <v>6845947</v>
+        <v>6846079</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764349</v>
+        <v>129764173</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>78838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535598</v>
+        <v>535509</v>
       </c>
       <c r="R6" t="n">
-        <v>6846065</v>
+        <v>6845947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764363</v>
+        <v>129764337</v>
       </c>
       <c r="B7" t="n">
-        <v>92046</v>
+        <v>75193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535632</v>
+        <v>535577</v>
       </c>
       <c r="R7" t="n">
-        <v>6846079</v>
+        <v>6846056</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129764256</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>129764213</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129764182</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>129764358</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129764178</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129764166</v>
       </c>
       <c r="B20" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764187</v>
+        <v>129764223</v>
       </c>
       <c r="B21" t="n">
-        <v>97020</v>
+        <v>91597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,27 +2687,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2715,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535460</v>
+        <v>535470</v>
       </c>
       <c r="R21" t="n">
-        <v>6845848</v>
+        <v>6845918</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2781,7 +2780,7 @@
         <v>129764331</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,10 +2878,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129764223</v>
+        <v>129764187</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>97024</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,26 +2889,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535470</v>
+        <v>535460</v>
       </c>
       <c r="R23" t="n">
-        <v>6845918</v>
+        <v>6845848</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,7 +2983,7 @@
         <v>129764320</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>129764343</v>
       </c>
       <c r="B29" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>129764159</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>129764312</v>
       </c>
       <c r="B32" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>129764388</v>
       </c>
       <c r="B33" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>129764168</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>129764275</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>129764302</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>129764334</v>
       </c>
       <c r="B3" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129764349</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129764363</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764173</v>
+        <v>129764337</v>
       </c>
       <c r="B6" t="n">
-        <v>78838</v>
+        <v>75193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535509</v>
+        <v>535577</v>
       </c>
       <c r="R6" t="n">
-        <v>6845947</v>
+        <v>6846056</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764337</v>
+        <v>129764173</v>
       </c>
       <c r="B7" t="n">
-        <v>75193</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535577</v>
+        <v>535509</v>
       </c>
       <c r="R7" t="n">
-        <v>6846056</v>
+        <v>6845947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764256</v>
+        <v>129764213</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535430</v>
+        <v>535466</v>
       </c>
       <c r="R9" t="n">
-        <v>6845927</v>
+        <v>6845930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764213</v>
+        <v>129764256</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535466</v>
+        <v>535430</v>
       </c>
       <c r="R10" t="n">
-        <v>6845930</v>
+        <v>6845927</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
         <v>129764182</v>
       </c>
       <c r="B12" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>129764358</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129764178</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764208</v>
+        <v>129764210</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,31 +2265,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535515</v>
+        <v>535529</v>
       </c>
       <c r="R17" t="n">
-        <v>6845927</v>
+        <v>6845938</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,17 +2330,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129764210</v>
+        <v>129764208</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,26 +2366,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2402,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535529</v>
+        <v>535515</v>
       </c>
       <c r="R18" t="n">
-        <v>6845938</v>
+        <v>6845927</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,13 +2436,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129764166</v>
       </c>
       <c r="B20" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764223</v>
+        <v>129764187</v>
       </c>
       <c r="B21" t="n">
-        <v>91597</v>
+        <v>97026</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,26 +2687,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2714,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535470</v>
+        <v>535460</v>
       </c>
       <c r="R21" t="n">
-        <v>6845918</v>
+        <v>6845848</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2780,7 +2781,7 @@
         <v>129764331</v>
       </c>
       <c r="B22" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2878,10 +2879,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129764187</v>
+        <v>129764223</v>
       </c>
       <c r="B23" t="n">
-        <v>97024</v>
+        <v>91599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2889,27 +2890,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535460</v>
+        <v>535470</v>
       </c>
       <c r="R23" t="n">
-        <v>6845848</v>
+        <v>6845918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,7 +2983,7 @@
         <v>129764320</v>
       </c>
       <c r="B24" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B29" t="n">
-        <v>91895</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,26 +3541,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3568,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R29" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,13 +3611,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3631,10 +3640,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91897</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3642,31 +3651,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R30" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,17 +3716,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>129764159</v>
       </c>
       <c r="B31" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>129764312</v>
       </c>
       <c r="B32" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>129764388</v>
       </c>
       <c r="B33" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>129764168</v>
       </c>
       <c r="B34" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>129764275</v>
       </c>
       <c r="B35" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>129764302</v>
       </c>
       <c r="B36" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -2676,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764187</v>
+        <v>129764331</v>
       </c>
       <c r="B21" t="n">
-        <v>97026</v>
+        <v>91599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,27 +2687,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2715,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535460</v>
+        <v>535494</v>
       </c>
       <c r="R21" t="n">
-        <v>6845848</v>
+        <v>6846030</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2777,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764331</v>
+        <v>129764223</v>
       </c>
       <c r="B22" t="n">
         <v>91599</v>
@@ -2816,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535494</v>
+        <v>535470</v>
       </c>
       <c r="R22" t="n">
-        <v>6846030</v>
+        <v>6845918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,10 +2878,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129764223</v>
+        <v>129764187</v>
       </c>
       <c r="B23" t="n">
-        <v>91599</v>
+        <v>97026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,26 +2889,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535470</v>
+        <v>535460</v>
       </c>
       <c r="R23" t="n">
-        <v>6845918</v>
+        <v>6845848</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764320</v>
+        <v>129764255</v>
       </c>
       <c r="B24" t="n">
-        <v>91897</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,26 +2991,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3018,10 +3023,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535446</v>
+        <v>535439</v>
       </c>
       <c r="R24" t="n">
-        <v>6846015</v>
+        <v>6845944</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,13 +3061,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3081,7 +3090,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129764255</v>
+        <v>129761739</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3109,12 +3118,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3124,13 +3141,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535439</v>
+        <v>535518</v>
       </c>
       <c r="R25" t="n">
-        <v>6845944</v>
+        <v>6845875</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3157,14 +3174,24 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3191,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129761739</v>
+        <v>129764320</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>91897</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3202,39 +3229,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3242,13 +3256,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535518</v>
+        <v>535446</v>
       </c>
       <c r="R26" t="n">
-        <v>6845875</v>
+        <v>6846015</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3275,32 +3289,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3319,37 +3319,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129764299</v>
+        <v>129764260</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3357,10 +3366,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535408</v>
+        <v>535417</v>
       </c>
       <c r="R27" t="n">
-        <v>6845995</v>
+        <v>6845933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,46 +3429,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764260</v>
+        <v>129764299</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>78838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535417</v>
+        <v>535408</v>
       </c>
       <c r="R28" t="n">
-        <v>6845933</v>
+        <v>6845995</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764213</v>
+        <v>129764256</v>
       </c>
       <c r="B9" t="n">
         <v>98780</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535466</v>
+        <v>535430</v>
       </c>
       <c r="R9" t="n">
-        <v>6845930</v>
+        <v>6845927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764256</v>
+        <v>129764213</v>
       </c>
       <c r="B10" t="n">
         <v>98780</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535430</v>
+        <v>535466</v>
       </c>
       <c r="R10" t="n">
-        <v>6845927</v>
+        <v>6845930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -2980,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764255</v>
+        <v>129764320</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>91897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,31 +2991,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3023,10 +3018,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535439</v>
+        <v>535446</v>
       </c>
       <c r="R24" t="n">
-        <v>6845944</v>
+        <v>6846015</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,17 +3056,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3090,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129761739</v>
+        <v>129764255</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3118,20 +3109,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3141,13 +3124,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535518</v>
+        <v>535439</v>
       </c>
       <c r="R25" t="n">
-        <v>6845875</v>
+        <v>6845944</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3174,24 +3157,14 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129764320</v>
+        <v>129761739</v>
       </c>
       <c r="B26" t="n">
-        <v>91897</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,26 +3202,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3256,13 +3242,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535446</v>
+        <v>535518</v>
       </c>
       <c r="R26" t="n">
-        <v>6846015</v>
+        <v>6845875</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3289,18 +3275,32 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -1407,7 +1407,7 @@
         <v>129764256</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>129764213</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129764178</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2777,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764223</v>
+        <v>129764187</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>97036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,26 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2815,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535470</v>
+        <v>535460</v>
       </c>
       <c r="R22" t="n">
-        <v>6845918</v>
+        <v>6845848</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,10 +2879,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129764187</v>
+        <v>129764223</v>
       </c>
       <c r="B23" t="n">
-        <v>97026</v>
+        <v>91599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2889,27 +2890,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535460</v>
+        <v>535470</v>
       </c>
       <c r="R23" t="n">
-        <v>6845848</v>
+        <v>6845918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764320</v>
+        <v>129764255</v>
       </c>
       <c r="B24" t="n">
-        <v>91897</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,26 +2991,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3018,10 +3023,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535446</v>
+        <v>535439</v>
       </c>
       <c r="R24" t="n">
-        <v>6846015</v>
+        <v>6845944</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,13 +3061,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3081,7 +3090,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129764255</v>
+        <v>129761739</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3109,12 +3118,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3124,13 +3141,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535439</v>
+        <v>535518</v>
       </c>
       <c r="R25" t="n">
-        <v>6845944</v>
+        <v>6845875</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3157,14 +3174,24 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3191,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129761739</v>
+        <v>129764320</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>91897</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3202,39 +3229,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3242,13 +3256,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535518</v>
+        <v>535446</v>
       </c>
       <c r="R26" t="n">
-        <v>6845875</v>
+        <v>6846015</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3275,32 +3289,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3319,46 +3319,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129764260</v>
+        <v>129764299</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>78838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3366,10 +3357,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535417</v>
+        <v>535408</v>
       </c>
       <c r="R27" t="n">
-        <v>6845933</v>
+        <v>6845995</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,37 +3420,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764299</v>
+        <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>78838</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535408</v>
+        <v>535417</v>
       </c>
       <c r="R28" t="n">
-        <v>6845995</v>
+        <v>6845933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,31 +3541,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3573,10 +3568,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R29" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,17 +3606,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3640,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B30" t="n">
-        <v>91897</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3651,26 +3642,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3678,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R30" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,13 +3712,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3943,36 +3943,44 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764388</v>
+        <v>129764275</v>
       </c>
       <c r="B33" t="n">
-        <v>97026</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -3982,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535670</v>
+        <v>535415</v>
       </c>
       <c r="R33" t="n">
-        <v>6846121</v>
+        <v>6845934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,37 +4053,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764168</v>
+        <v>129764302</v>
       </c>
       <c r="B34" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4083,10 +4100,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535523</v>
+        <v>535410</v>
       </c>
       <c r="R34" t="n">
-        <v>6845943</v>
+        <v>6845976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,44 +4163,36 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764275</v>
+        <v>129764388</v>
       </c>
       <c r="B35" t="n">
-        <v>98780</v>
+        <v>97036</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4193,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535415</v>
+        <v>535670</v>
       </c>
       <c r="R35" t="n">
-        <v>6845934</v>
+        <v>6846121</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,46 +4265,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129764302</v>
+        <v>129764168</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535410</v>
+        <v>535523</v>
       </c>
       <c r="R36" t="n">
-        <v>6845976</v>
+        <v>6845943</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129761686</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>129764334</v>
       </c>
       <c r="B3" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129764349</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129764363</v>
       </c>
       <c r="B5" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>129764337</v>
       </c>
       <c r="B6" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>129764173</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129764256</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>129764213</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>129764154</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129764182</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>129764358</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129764178</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764210</v>
+        <v>129764208</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,26 +2265,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2292,10 +2297,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535529</v>
+        <v>535515</v>
       </c>
       <c r="R17" t="n">
-        <v>6845938</v>
+        <v>6845927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,13 +2335,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2355,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129764208</v>
+        <v>129764210</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,31 +2375,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2398,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535515</v>
+        <v>535529</v>
       </c>
       <c r="R18" t="n">
-        <v>6845927</v>
+        <v>6845938</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,17 +2440,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129764166</v>
       </c>
       <c r="B20" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>129764331</v>
       </c>
       <c r="B21" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129764187</v>
       </c>
       <c r="B22" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129764223</v>
       </c>
       <c r="B23" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>129764320</v>
       </c>
       <c r="B24" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129764255</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>129761739</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>129764299</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B29" t="n">
-        <v>91897</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,26 +3541,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3568,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R29" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,13 +3611,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3631,10 +3640,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3642,31 +3651,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R30" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,17 +3716,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129764159</v>
+        <v>129764312</v>
       </c>
       <c r="B31" t="n">
-        <v>91599</v>
+        <v>91900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,21 +3752,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535563</v>
+        <v>535470</v>
       </c>
       <c r="R31" t="n">
-        <v>6845935</v>
+        <v>6845980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129764312</v>
+        <v>129764159</v>
       </c>
       <c r="B32" t="n">
-        <v>91897</v>
+        <v>91602</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535470</v>
+        <v>535563</v>
       </c>
       <c r="R32" t="n">
-        <v>6845980</v>
+        <v>6845935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3943,44 +3943,36 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764275</v>
+        <v>129764388</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>97040</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -3990,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535415</v>
+        <v>535670</v>
       </c>
       <c r="R33" t="n">
-        <v>6845934</v>
+        <v>6846121</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4053,46 +4045,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764302</v>
+        <v>129764168</v>
       </c>
       <c r="B34" t="n">
-        <v>98790</v>
+        <v>91602</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4100,10 +4083,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535410</v>
+        <v>535523</v>
       </c>
       <c r="R34" t="n">
-        <v>6845976</v>
+        <v>6845943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4163,36 +4146,44 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764388</v>
+        <v>129764275</v>
       </c>
       <c r="B35" t="n">
-        <v>97036</v>
+        <v>98794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4202,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535670</v>
+        <v>535415</v>
       </c>
       <c r="R35" t="n">
-        <v>6846121</v>
+        <v>6845934</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4265,37 +4256,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129764168</v>
+        <v>129764302</v>
       </c>
       <c r="B36" t="n">
-        <v>91599</v>
+        <v>98794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535523</v>
+        <v>535410</v>
       </c>
       <c r="R36" t="n">
-        <v>6845943</v>
+        <v>6845976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
         <v>129761765</v>
       </c>
       <c r="B37" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764349</v>
+        <v>129764337</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>75196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535598</v>
+        <v>535577</v>
       </c>
       <c r="R4" t="n">
-        <v>6846065</v>
+        <v>6846056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764363</v>
+        <v>129764173</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535632</v>
+        <v>535509</v>
       </c>
       <c r="R5" t="n">
-        <v>6846079</v>
+        <v>6845947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764337</v>
+        <v>129764349</v>
       </c>
       <c r="B6" t="n">
-        <v>75196</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535577</v>
+        <v>535598</v>
       </c>
       <c r="R6" t="n">
-        <v>6846056</v>
+        <v>6846065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764173</v>
+        <v>129764363</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>92055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535509</v>
+        <v>535632</v>
       </c>
       <c r="R7" t="n">
-        <v>6845947</v>
+        <v>6846079</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764320</v>
+        <v>129764255</v>
       </c>
       <c r="B24" t="n">
-        <v>91900</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,26 +2991,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3018,10 +3023,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535446</v>
+        <v>535439</v>
       </c>
       <c r="R24" t="n">
-        <v>6846015</v>
+        <v>6845944</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,13 +3061,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3081,10 +3090,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129764255</v>
+        <v>129764320</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>91900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,31 +3101,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3124,10 +3128,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535439</v>
+        <v>535446</v>
       </c>
       <c r="R25" t="n">
-        <v>6845944</v>
+        <v>6846015</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,17 +3166,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3319,37 +3319,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129764299</v>
+        <v>129764260</v>
       </c>
       <c r="B27" t="n">
-        <v>78841</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3357,10 +3366,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535408</v>
+        <v>535417</v>
       </c>
       <c r="R27" t="n">
-        <v>6845995</v>
+        <v>6845933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,46 +3429,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764260</v>
+        <v>129764299</v>
       </c>
       <c r="B28" t="n">
-        <v>98794</v>
+        <v>78841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535417</v>
+        <v>535408</v>
       </c>
       <c r="R28" t="n">
-        <v>6845933</v>
+        <v>6845995</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3943,36 +3943,44 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764388</v>
+        <v>129764275</v>
       </c>
       <c r="B33" t="n">
-        <v>97040</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -3982,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535670</v>
+        <v>535415</v>
       </c>
       <c r="R33" t="n">
-        <v>6846121</v>
+        <v>6845934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764168</v>
+        <v>129764388</v>
       </c>
       <c r="B34" t="n">
-        <v>91602</v>
+        <v>97040</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4056,26 +4064,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4083,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535523</v>
+        <v>535670</v>
       </c>
       <c r="R34" t="n">
-        <v>6845943</v>
+        <v>6846121</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,46 +4155,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764275</v>
+        <v>129764168</v>
       </c>
       <c r="B35" t="n">
-        <v>98794</v>
+        <v>91602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535415</v>
+        <v>535523</v>
       </c>
       <c r="R35" t="n">
-        <v>6845934</v>
+        <v>6845943</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764337</v>
+        <v>129764349</v>
       </c>
       <c r="B4" t="n">
-        <v>75196</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535577</v>
+        <v>535598</v>
       </c>
       <c r="R4" t="n">
-        <v>6846056</v>
+        <v>6846065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764173</v>
+        <v>129764363</v>
       </c>
       <c r="B5" t="n">
-        <v>78841</v>
+        <v>92055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535509</v>
+        <v>535632</v>
       </c>
       <c r="R5" t="n">
-        <v>6845947</v>
+        <v>6846079</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764349</v>
+        <v>129764337</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>75196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535598</v>
+        <v>535577</v>
       </c>
       <c r="R6" t="n">
-        <v>6846065</v>
+        <v>6846056</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764363</v>
+        <v>129764173</v>
       </c>
       <c r="B7" t="n">
-        <v>92055</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535632</v>
+        <v>535509</v>
       </c>
       <c r="R7" t="n">
-        <v>6846079</v>
+        <v>6845947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764255</v>
+        <v>129761739</v>
       </c>
       <c r="B24" t="n">
         <v>57737</v>
@@ -3008,12 +3008,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3023,13 +3031,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535439</v>
+        <v>535518</v>
       </c>
       <c r="R24" t="n">
-        <v>6845944</v>
+        <v>6845875</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3056,14 +3064,24 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3090,10 +3108,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129764320</v>
+        <v>129764255</v>
       </c>
       <c r="B25" t="n">
-        <v>91900</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,26 +3119,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3128,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535446</v>
+        <v>535439</v>
       </c>
       <c r="R25" t="n">
-        <v>6846015</v>
+        <v>6845944</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3166,13 +3189,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3191,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129761739</v>
+        <v>129764320</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>91900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3202,39 +3229,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3242,13 +3256,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535518</v>
+        <v>535446</v>
       </c>
       <c r="R26" t="n">
-        <v>6845875</v>
+        <v>6846015</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3275,32 +3289,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3943,44 +3943,36 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764275</v>
+        <v>129764388</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>97040</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -3990,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535415</v>
+        <v>535670</v>
       </c>
       <c r="R33" t="n">
-        <v>6845934</v>
+        <v>6846121</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4053,10 +4045,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764388</v>
+        <v>129764168</v>
       </c>
       <c r="B34" t="n">
-        <v>97040</v>
+        <v>91602</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,27 +4056,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4092,10 +4083,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535670</v>
+        <v>535523</v>
       </c>
       <c r="R34" t="n">
-        <v>6846121</v>
+        <v>6845943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4155,37 +4146,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764168</v>
+        <v>129764275</v>
       </c>
       <c r="B35" t="n">
-        <v>91602</v>
+        <v>98794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535523</v>
+        <v>535415</v>
       </c>
       <c r="R35" t="n">
-        <v>6845943</v>
+        <v>6845934</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129761686</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>129764334</v>
       </c>
       <c r="B3" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129764349</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129764363</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>129764337</v>
       </c>
       <c r="B6" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>129764173</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129764256</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>129764213</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>129764154</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129764182</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>129764285</v>
       </c>
       <c r="B13" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>129764358</v>
       </c>
       <c r="B14" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129764178</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129764208</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>129764210</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129764166</v>
       </c>
       <c r="B20" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>129764331</v>
       </c>
       <c r="B21" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129764187</v>
       </c>
       <c r="B22" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129764223</v>
       </c>
       <c r="B23" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129761739</v>
+        <v>129764320</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>91903</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,39 +2991,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3031,13 +3018,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535518</v>
+        <v>535446</v>
       </c>
       <c r="R24" t="n">
-        <v>6845875</v>
+        <v>6846015</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3064,32 +3051,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3111,7 +3084,7 @@
         <v>129764255</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129764320</v>
+        <v>129761739</v>
       </c>
       <c r="B26" t="n">
-        <v>91900</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,26 +3202,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3256,13 +3242,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535446</v>
+        <v>535518</v>
       </c>
       <c r="R26" t="n">
-        <v>6846015</v>
+        <v>6845875</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3289,18 +3275,32 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3319,46 +3319,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129764260</v>
+        <v>129764299</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>78844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3366,10 +3357,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535417</v>
+        <v>535408</v>
       </c>
       <c r="R27" t="n">
-        <v>6845933</v>
+        <v>6845995</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,37 +3420,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764299</v>
+        <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>78841</v>
+        <v>98797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535408</v>
+        <v>535417</v>
       </c>
       <c r="R28" t="n">
-        <v>6845995</v>
+        <v>6845933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>91903</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,31 +3541,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3573,10 +3568,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R29" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,17 +3606,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3640,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B30" t="n">
-        <v>91900</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3651,26 +3642,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3678,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R30" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,13 +3712,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>129764312</v>
       </c>
       <c r="B31" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>129764159</v>
       </c>
       <c r="B32" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>129764388</v>
       </c>
       <c r="B33" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>129764168</v>
       </c>
       <c r="B34" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>129764275</v>
       </c>
       <c r="B35" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>129764302</v>
       </c>
       <c r="B36" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>129761765</v>
       </c>
       <c r="B37" t="n">
-        <v>57841</v>
+        <v>57844</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -2254,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764208</v>
+        <v>129764210</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,31 +2265,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535515</v>
+        <v>535529</v>
       </c>
       <c r="R17" t="n">
-        <v>6845927</v>
+        <v>6845938</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,17 +2330,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129764210</v>
+        <v>129764208</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,26 +2366,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2402,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535529</v>
+        <v>535515</v>
       </c>
       <c r="R18" t="n">
-        <v>6845938</v>
+        <v>6845927</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,13 +2436,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>129764334</v>
       </c>
       <c r="B3" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764349</v>
+        <v>129764337</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>75199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535598</v>
+        <v>535577</v>
       </c>
       <c r="R4" t="n">
-        <v>6846065</v>
+        <v>6846056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764363</v>
+        <v>129764173</v>
       </c>
       <c r="B5" t="n">
-        <v>92058</v>
+        <v>78845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535632</v>
+        <v>535509</v>
       </c>
       <c r="R5" t="n">
-        <v>6846079</v>
+        <v>6845947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764337</v>
+        <v>129764349</v>
       </c>
       <c r="B6" t="n">
-        <v>75199</v>
+        <v>91606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535577</v>
+        <v>535598</v>
       </c>
       <c r="R6" t="n">
-        <v>6846056</v>
+        <v>6846065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764173</v>
+        <v>129764363</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>92059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535509</v>
+        <v>535632</v>
       </c>
       <c r="R7" t="n">
-        <v>6845947</v>
+        <v>6846079</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129764256</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>129764213</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>129764154</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129764182</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>129764358</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129764178</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129764210</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129764166</v>
       </c>
       <c r="B20" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764331</v>
+        <v>129764187</v>
       </c>
       <c r="B21" t="n">
-        <v>91605</v>
+        <v>97044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,26 +2687,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2714,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535494</v>
+        <v>535460</v>
       </c>
       <c r="R21" t="n">
-        <v>6846030</v>
+        <v>6845848</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,10 +2778,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764187</v>
+        <v>129764223</v>
       </c>
       <c r="B22" t="n">
-        <v>97043</v>
+        <v>91606</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,27 +2789,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535460</v>
+        <v>535470</v>
       </c>
       <c r="R22" t="n">
-        <v>6845848</v>
+        <v>6845918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129764223</v>
+        <v>129764331</v>
       </c>
       <c r="B23" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535470</v>
+        <v>535494</v>
       </c>
       <c r="R23" t="n">
-        <v>6845918</v>
+        <v>6846030</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764320</v>
+        <v>129761739</v>
       </c>
       <c r="B24" t="n">
-        <v>91903</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,26 +2991,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3018,13 +3031,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535446</v>
+        <v>535518</v>
       </c>
       <c r="R24" t="n">
-        <v>6846015</v>
+        <v>6845875</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3051,18 +3064,32 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3191,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129761739</v>
+        <v>129764320</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>91904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3202,39 +3229,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3242,13 +3256,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535518</v>
+        <v>535446</v>
       </c>
       <c r="R26" t="n">
-        <v>6845875</v>
+        <v>6846015</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3275,32 +3289,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>129764299</v>
       </c>
       <c r="B27" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B29" t="n">
-        <v>91903</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,26 +3541,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3568,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R29" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,13 +3611,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3631,10 +3640,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>91904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3642,31 +3651,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3674,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R30" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,17 +3716,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>129764312</v>
       </c>
       <c r="B31" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>129764159</v>
       </c>
       <c r="B32" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3943,10 +3943,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764388</v>
+        <v>129764168</v>
       </c>
       <c r="B33" t="n">
-        <v>97043</v>
+        <v>91606</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,27 +3954,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3982,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535670</v>
+        <v>535523</v>
       </c>
       <c r="R33" t="n">
-        <v>6846121</v>
+        <v>6845943</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,10 +4044,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764168</v>
+        <v>129764388</v>
       </c>
       <c r="B34" t="n">
-        <v>91605</v>
+        <v>97044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4056,26 +4055,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535523</v>
+        <v>535670</v>
       </c>
       <c r="R34" t="n">
-        <v>6845943</v>
+        <v>6846121</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,7 +4149,7 @@
         <v>129764275</v>
       </c>
       <c r="B35" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>129764302</v>
       </c>
       <c r="B36" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -1303,37 +1303,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129764308</v>
+        <v>129764256</v>
       </c>
       <c r="B8" t="n">
-        <v>91627</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1341,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535447</v>
+        <v>535430</v>
       </c>
       <c r="R8" t="n">
-        <v>6845978</v>
+        <v>6845927</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1413,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764256</v>
+        <v>129764213</v>
       </c>
       <c r="B9" t="n">
         <v>98798</v>
@@ -1434,7 +1443,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1451,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535430</v>
+        <v>535466</v>
       </c>
       <c r="R9" t="n">
-        <v>6845927</v>
+        <v>6845930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,46 +1523,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764213</v>
+        <v>129764308</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>91627</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535466</v>
+        <v>535447</v>
       </c>
       <c r="R10" t="n">
-        <v>6845930</v>
+        <v>6845978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3108,10 +3108,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129764255</v>
+        <v>129764320</v>
       </c>
       <c r="B25" t="n">
-        <v>57740</v>
+        <v>91904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3119,31 +3119,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3151,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535439</v>
+        <v>535446</v>
       </c>
       <c r="R25" t="n">
-        <v>6845944</v>
+        <v>6846015</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,17 +3184,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3218,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129764320</v>
+        <v>129764255</v>
       </c>
       <c r="B26" t="n">
-        <v>91904</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,26 +3220,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3256,10 +3252,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535446</v>
+        <v>535439</v>
       </c>
       <c r="R26" t="n">
-        <v>6846015</v>
+        <v>6845944</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,13 +3290,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -1303,46 +1303,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129764256</v>
+        <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>91627</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1350,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535430</v>
+        <v>535447</v>
       </c>
       <c r="R8" t="n">
-        <v>6845927</v>
+        <v>6845978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764213</v>
+        <v>129764256</v>
       </c>
       <c r="B9" t="n">
         <v>98798</v>
@@ -1443,7 +1434,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1460,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535466</v>
+        <v>535430</v>
       </c>
       <c r="R9" t="n">
-        <v>6845930</v>
+        <v>6845927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,37 +1514,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764308</v>
+        <v>129764213</v>
       </c>
       <c r="B10" t="n">
-        <v>91627</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535447</v>
+        <v>535466</v>
       </c>
       <c r="R10" t="n">
-        <v>6845978</v>
+        <v>6845930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3108,10 +3108,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129764320</v>
+        <v>129764255</v>
       </c>
       <c r="B25" t="n">
-        <v>91904</v>
+        <v>57740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3119,26 +3119,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3146,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535446</v>
+        <v>535439</v>
       </c>
       <c r="R25" t="n">
-        <v>6846015</v>
+        <v>6845944</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3184,13 +3189,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3209,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129764255</v>
+        <v>129764320</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>91904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,31 +3229,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3252,10 +3256,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535439</v>
+        <v>535446</v>
       </c>
       <c r="R26" t="n">
-        <v>6845944</v>
+        <v>6846015</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,17 +3294,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129761686</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>129764334</v>
       </c>
       <c r="B3" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129764337</v>
       </c>
       <c r="B4" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764173</v>
+        <v>129764349</v>
       </c>
       <c r="B5" t="n">
-        <v>78845</v>
+        <v>91623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535509</v>
+        <v>535598</v>
       </c>
       <c r="R5" t="n">
-        <v>6845947</v>
+        <v>6846065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764349</v>
+        <v>129764363</v>
       </c>
       <c r="B6" t="n">
-        <v>91606</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535598</v>
+        <v>535632</v>
       </c>
       <c r="R6" t="n">
-        <v>6846065</v>
+        <v>6846079</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764363</v>
+        <v>129764173</v>
       </c>
       <c r="B7" t="n">
-        <v>92059</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535632</v>
+        <v>535509</v>
       </c>
       <c r="R7" t="n">
-        <v>6846079</v>
+        <v>6845947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>129764308</v>
       </c>
       <c r="B8" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129764256</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>129764213</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>129764154</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129764182</v>
       </c>
       <c r="B12" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>129764358</v>
       </c>
       <c r="B14" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>129764380</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129764178</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129764210</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>129764305</v>
       </c>
       <c r="B19" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129764166</v>
       </c>
       <c r="B20" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764187</v>
+        <v>129764331</v>
       </c>
       <c r="B21" t="n">
-        <v>97044</v>
+        <v>91623</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2687,27 +2687,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2715,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535460</v>
+        <v>535494</v>
       </c>
       <c r="R21" t="n">
-        <v>6845848</v>
+        <v>6846030</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764223</v>
+        <v>129764187</v>
       </c>
       <c r="B22" t="n">
-        <v>91606</v>
+        <v>97061</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,26 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535470</v>
+        <v>535460</v>
       </c>
       <c r="R22" t="n">
-        <v>6845918</v>
+        <v>6845848</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129764331</v>
+        <v>129764223</v>
       </c>
       <c r="B23" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535494</v>
+        <v>535470</v>
       </c>
       <c r="R23" t="n">
-        <v>6846030</v>
+        <v>6845918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129761739</v>
+        <v>129764320</v>
       </c>
       <c r="B24" t="n">
-        <v>57740</v>
+        <v>91921</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,39 +2991,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3031,13 +3018,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535518</v>
+        <v>535446</v>
       </c>
       <c r="R24" t="n">
-        <v>6845875</v>
+        <v>6846015</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3064,32 +3051,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3218,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129764320</v>
+        <v>129761739</v>
       </c>
       <c r="B26" t="n">
-        <v>91904</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,26 +3202,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3256,13 +3242,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535446</v>
+        <v>535518</v>
       </c>
       <c r="R26" t="n">
-        <v>6846015</v>
+        <v>6845875</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3289,18 +3275,32 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>129764299</v>
       </c>
       <c r="B27" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>129764260</v>
       </c>
       <c r="B28" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764374</v>
+        <v>129764343</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>91921</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,31 +3541,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3573,10 +3568,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535655</v>
+        <v>535587</v>
       </c>
       <c r="R29" t="n">
-        <v>6846098</v>
+        <v>6846066</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,17 +3606,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3640,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B30" t="n">
-        <v>91904</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3651,26 +3642,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3678,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R30" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,13 +3712,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>129764312</v>
       </c>
       <c r="B31" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>129764159</v>
       </c>
       <c r="B32" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3943,37 +3943,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764168</v>
+        <v>129764275</v>
       </c>
       <c r="B33" t="n">
-        <v>91606</v>
+        <v>98815</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3981,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535523</v>
+        <v>535415</v>
       </c>
       <c r="R33" t="n">
-        <v>6845943</v>
+        <v>6845934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,36 +4053,44 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764388</v>
+        <v>129764302</v>
       </c>
       <c r="B34" t="n">
-        <v>97044</v>
+        <v>98815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4083,10 +4100,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535670</v>
+        <v>535410</v>
       </c>
       <c r="R34" t="n">
-        <v>6846121</v>
+        <v>6845976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,44 +4163,36 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764275</v>
+        <v>129764388</v>
       </c>
       <c r="B35" t="n">
-        <v>98798</v>
+        <v>97061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4193,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535415</v>
+        <v>535670</v>
       </c>
       <c r="R35" t="n">
-        <v>6845934</v>
+        <v>6846121</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,46 +4265,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129764302</v>
+        <v>129764168</v>
       </c>
       <c r="B36" t="n">
-        <v>98798</v>
+        <v>91623</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535410</v>
+        <v>535523</v>
       </c>
       <c r="R36" t="n">
-        <v>6845976</v>
+        <v>6845943</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -1303,37 +1303,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129764308</v>
+        <v>129764256</v>
       </c>
       <c r="B8" t="n">
-        <v>91660</v>
+        <v>98831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1341,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535447</v>
+        <v>535430</v>
       </c>
       <c r="R8" t="n">
-        <v>6845978</v>
+        <v>6845927</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1413,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764256</v>
+        <v>129764213</v>
       </c>
       <c r="B9" t="n">
         <v>98831</v>
@@ -1434,7 +1443,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1451,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535430</v>
+        <v>535466</v>
       </c>
       <c r="R9" t="n">
-        <v>6845927</v>
+        <v>6845930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,46 +1523,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764213</v>
+        <v>129764308</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>91660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535466</v>
+        <v>535447</v>
       </c>
       <c r="R10" t="n">
-        <v>6845930</v>
+        <v>6845978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764223</v>
+        <v>129764187</v>
       </c>
       <c r="B21" t="n">
-        <v>91639</v>
+        <v>97077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,26 +2678,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2705,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535470</v>
+        <v>535460</v>
       </c>
       <c r="R21" t="n">
-        <v>6845918</v>
+        <v>6845848</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,10 +2769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764187</v>
+        <v>129764223</v>
       </c>
       <c r="B22" t="n">
-        <v>97077</v>
+        <v>91639</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,27 +2780,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535460</v>
+        <v>535470</v>
       </c>
       <c r="R22" t="n">
-        <v>6845848</v>
+        <v>6845918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -3911,7 +3911,7 @@
         <v>129764208</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>129764255</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>129761739</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>129764374</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>129761765</v>
       </c>
       <c r="B37" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -3911,7 +3911,7 @@
         <v>129764208</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>129764255</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>129761739</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>129764374</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>129761765</v>
       </c>
       <c r="B37" t="n">
-        <v>57930</v>
+        <v>57956</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -4018,7 +4018,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129764255</v>
+        <v>129761739</v>
       </c>
       <c r="B34" t="n">
         <v>57852</v>
@@ -4046,12 +4046,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4061,13 +4069,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535439</v>
+        <v>535518</v>
       </c>
       <c r="R34" t="n">
-        <v>6845944</v>
+        <v>6845875</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4094,14 +4102,24 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4128,7 +4146,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129761739</v>
+        <v>129764255</v>
       </c>
       <c r="B35" t="n">
         <v>57852</v>
@@ -4156,20 +4174,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4179,13 +4189,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535518</v>
+        <v>535439</v>
       </c>
       <c r="R35" t="n">
-        <v>6845875</v>
+        <v>6845944</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4212,24 +4222,14 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129761686</v>
+        <v>129764187</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535552</v>
+        <v>535460</v>
       </c>
       <c r="R2" t="n">
-        <v>6846061</v>
+        <v>6845848</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +747,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -798,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129764334</v>
+        <v>129764388</v>
       </c>
       <c r="B3" t="n">
-        <v>91937</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,26 +788,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535492</v>
+        <v>535670</v>
       </c>
       <c r="R3" t="n">
-        <v>6846029</v>
+        <v>6846121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129764349</v>
+        <v>129764166</v>
       </c>
       <c r="B4" t="n">
-        <v>91639</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535598</v>
+        <v>535555</v>
       </c>
       <c r="R4" t="n">
-        <v>6846065</v>
+        <v>6845967</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129764363</v>
+        <v>129764312</v>
       </c>
       <c r="B5" t="n">
-        <v>92092</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535632</v>
+        <v>535470</v>
       </c>
       <c r="R5" t="n">
-        <v>6846079</v>
+        <v>6845980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129764337</v>
+        <v>129764320</v>
       </c>
       <c r="B6" t="n">
-        <v>75201</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535577</v>
+        <v>535446</v>
       </c>
       <c r="R6" t="n">
-        <v>6846056</v>
+        <v>6846015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,10 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129764173</v>
+        <v>129764334</v>
       </c>
       <c r="B7" t="n">
-        <v>78852</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,21 +1193,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535509</v>
+        <v>535492</v>
       </c>
       <c r="R7" t="n">
-        <v>6845947</v>
+        <v>6846029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,46 +1283,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129764256</v>
+        <v>129764343</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1350,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535430</v>
+        <v>535587</v>
       </c>
       <c r="R8" t="n">
-        <v>6845927</v>
+        <v>6846066</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,46 +1384,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129764213</v>
+        <v>129764159</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535466</v>
+        <v>535563</v>
       </c>
       <c r="R9" t="n">
-        <v>6845930</v>
+        <v>6845935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129764308</v>
+        <v>129764168</v>
       </c>
       <c r="B10" t="n">
-        <v>91660</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1496,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535447</v>
+        <v>535523</v>
       </c>
       <c r="R10" t="n">
-        <v>6845978</v>
+        <v>6845943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,10 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129764154</v>
+        <v>129764182</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535592</v>
+        <v>535475</v>
       </c>
       <c r="R11" t="n">
-        <v>6845934</v>
+        <v>6845922</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1687,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129764182</v>
+        <v>129764223</v>
       </c>
       <c r="B12" t="n">
-        <v>91639</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535475</v>
+        <v>535470</v>
       </c>
       <c r="R12" t="n">
-        <v>6845922</v>
+        <v>6845918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,43 +1788,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129764285</v>
+        <v>129764331</v>
       </c>
       <c r="B13" t="n">
-        <v>8440</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1870,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535385</v>
+        <v>535494</v>
       </c>
       <c r="R13" t="n">
-        <v>6845929</v>
+        <v>6846030</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129764358</v>
+        <v>129764349</v>
       </c>
       <c r="B14" t="n">
-        <v>91639</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535632</v>
+        <v>535598</v>
       </c>
       <c r="R14" t="n">
-        <v>6846079</v>
+        <v>6846065</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,46 +1990,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129764380</v>
+        <v>129764358</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2081,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535651</v>
+        <v>535632</v>
       </c>
       <c r="R15" t="n">
-        <v>6846125</v>
+        <v>6846079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,46 +2091,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129764178</v>
+        <v>129764363</v>
       </c>
       <c r="B16" t="n">
-        <v>98831</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2191,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535471</v>
+        <v>535632</v>
       </c>
       <c r="R16" t="n">
-        <v>6845973</v>
+        <v>6846079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,10 +2192,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129764210</v>
+        <v>129764308</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,21 +2203,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2292,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535529</v>
+        <v>535447</v>
       </c>
       <c r="R17" t="n">
-        <v>6845938</v>
+        <v>6845978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,10 +2293,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129764305</v>
+        <v>129764154</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,35 +2304,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2402,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535439</v>
+        <v>535592</v>
       </c>
       <c r="R18" t="n">
-        <v>6845968</v>
+        <v>6845934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,32 +2394,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129764166</v>
+        <v>129764210</v>
       </c>
       <c r="B19" t="n">
-        <v>91937</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2503,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535555</v>
+        <v>535529</v>
       </c>
       <c r="R19" t="n">
-        <v>6845967</v>
+        <v>6845938</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,10 +2495,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129764331</v>
+        <v>129764337</v>
       </c>
       <c r="B20" t="n">
-        <v>91639</v>
+        <v>75428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,21 +2506,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535494</v>
+        <v>535577</v>
       </c>
       <c r="R20" t="n">
-        <v>6846030</v>
+        <v>6846056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,10 +2596,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129764187</v>
+        <v>129764173</v>
       </c>
       <c r="B21" t="n">
-        <v>97077</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,27 +2607,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2706,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535460</v>
+        <v>535509</v>
       </c>
       <c r="R21" t="n">
-        <v>6845848</v>
+        <v>6845947</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,10 +2697,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129764223</v>
+        <v>129764299</v>
       </c>
       <c r="B22" t="n">
-        <v>91639</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,21 +2708,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2807,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535470</v>
+        <v>535408</v>
       </c>
       <c r="R22" t="n">
-        <v>6845918</v>
+        <v>6845995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,10 +2798,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129764320</v>
+        <v>129761739</v>
       </c>
       <c r="B23" t="n">
-        <v>91937</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2881,26 +2809,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2908,13 +2849,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535446</v>
+        <v>535518</v>
       </c>
       <c r="R23" t="n">
-        <v>6846015</v>
+        <v>6845875</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2941,18 +2882,32 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2971,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129764299</v>
+        <v>129764208</v>
       </c>
       <c r="B24" t="n">
-        <v>78852</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2982,26 +2937,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3009,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535408</v>
+        <v>535515</v>
       </c>
       <c r="R24" t="n">
-        <v>6845995</v>
+        <v>6845927</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,13 +3007,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack i gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3072,46 +3036,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129764260</v>
+        <v>129764255</v>
       </c>
       <c r="B25" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3119,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535417</v>
+        <v>535439</v>
       </c>
       <c r="R25" t="n">
-        <v>6845933</v>
+        <v>6845944</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,13 +3117,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3182,10 +3146,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129764343</v>
+        <v>129764374</v>
       </c>
       <c r="B26" t="n">
-        <v>91937</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3193,26 +3157,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3220,10 +3189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535587</v>
+        <v>535655</v>
       </c>
       <c r="R26" t="n">
-        <v>6846066</v>
+        <v>6846098</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,13 +3227,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3283,10 +3256,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129764312</v>
+        <v>129761686</v>
       </c>
       <c r="B27" t="n">
-        <v>91937</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,26 +3267,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3321,13 +3307,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>535470</v>
+        <v>535552</v>
       </c>
       <c r="R27" t="n">
-        <v>6845980</v>
+        <v>6846061</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3354,18 +3340,27 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3384,10 +3379,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129764159</v>
+        <v>129761765</v>
       </c>
       <c r="B28" t="n">
-        <v>91639</v>
+        <v>58057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3395,26 +3390,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3422,13 +3430,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535563</v>
+        <v>535524</v>
       </c>
       <c r="R28" t="n">
-        <v>6845935</v>
+        <v>6845867</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3455,18 +3463,32 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Har lavskrikan på film. ska länka när jag fått upp filmen på internet. https://youtu.be/GXFxs2jfycE</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,46 +3507,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129764275</v>
+        <v>129764285</v>
       </c>
       <c r="B29" t="n">
-        <v>98831</v>
+        <v>8444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3532,10 +3551,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>535415</v>
+        <v>535385</v>
       </c>
       <c r="R29" t="n">
-        <v>6845934</v>
+        <v>6845929</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3595,10 +3614,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129764302</v>
+        <v>129764178</v>
       </c>
       <c r="B30" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3625,7 +3644,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3642,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>535410</v>
+        <v>535471</v>
       </c>
       <c r="R30" t="n">
-        <v>6845976</v>
+        <v>6845973</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3705,36 +3724,44 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129764388</v>
+        <v>129764213</v>
       </c>
       <c r="B31" t="n">
-        <v>97077</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3744,10 +3771,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>535670</v>
+        <v>535466</v>
       </c>
       <c r="R31" t="n">
-        <v>6846121</v>
+        <v>6845930</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3807,37 +3834,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129764168</v>
+        <v>129764256</v>
       </c>
       <c r="B32" t="n">
-        <v>91639</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3845,10 +3881,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535523</v>
+        <v>535430</v>
       </c>
       <c r="R32" t="n">
-        <v>6845943</v>
+        <v>6845927</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,42 +3944,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129764208</v>
+        <v>129764260</v>
       </c>
       <c r="B33" t="n">
-        <v>57852</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3951,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535515</v>
+        <v>535417</v>
       </c>
       <c r="R33" t="n">
-        <v>6845927</v>
+        <v>6845933</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3989,17 +4029,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre spår av ringhack i gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4018,50 +4054,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129761739</v>
+        <v>129764275</v>
       </c>
       <c r="B34" t="n">
-        <v>57852</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4069,13 +4101,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535518</v>
+        <v>535415</v>
       </c>
       <c r="R34" t="n">
-        <v>6845875</v>
+        <v>6845934</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4102,32 +4134,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>En tretåig hackspett som är lite upprörd och varnar förmodligen lite irriterad på en lavskrika som far runt i granarna och födosöker samtidigt. Fick inte tretåig på bild men lyckades ta en inspelning med appen BirdNet. Jag fick även se den en kort stund så jag kunde artbestämma den själv.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4146,42 +4164,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129764255</v>
+        <v>129764302</v>
       </c>
       <c r="B35" t="n">
-        <v>57852</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4189,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>535439</v>
+        <v>535410</v>
       </c>
       <c r="R35" t="n">
-        <v>6845944</v>
+        <v>6845976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4227,17 +4249,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Troligtvis äldre bobyggeförsök  av tretåig hackspett på låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4256,42 +4274,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129764374</v>
+        <v>129764305</v>
       </c>
       <c r="B36" t="n">
-        <v>57852</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4299,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>535655</v>
+        <v>535439</v>
       </c>
       <c r="R36" t="n">
-        <v>6846098</v>
+        <v>6845968</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4337,17 +4359,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Troligen äldre bobygge försök av tretåig hackspett i låg höjd i gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4366,50 +4384,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129761765</v>
+        <v>129764380</v>
       </c>
       <c r="B37" t="n">
-        <v>57956</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4417,13 +4431,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>535524</v>
+        <v>535651</v>
       </c>
       <c r="R37" t="n">
-        <v>6845867</v>
+        <v>6846125</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4450,32 +4464,18 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Har lavskrikan på film. ska länka när jag fått upp filmen på internet. https://youtu.be/GXFxs2jfycE</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6734-2025 artfynd.xlsx
+++ b/artfynd/A 6734-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764187</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764388</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764166</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764312</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764320</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764334</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764343</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764159</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764168</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1684,6 +1734,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764182</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1785,6 +1840,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764223</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764331</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764349</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764358</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764363</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2290,6 +2370,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764308</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2391,6 +2476,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764154</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764210</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2593,6 +2688,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764337</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2694,6 +2794,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764173</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2795,6 +2900,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764299</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2923,6 +3033,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129761739</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3033,6 +3148,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764208</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3143,6 +3263,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764255</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3253,6 +3378,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764374</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3376,6 +3506,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129761686</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3504,6 +3639,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129761765</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3611,6 +3751,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764285</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3721,6 +3866,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764178</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3831,6 +3981,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764213</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3941,6 +4096,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764256</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4051,6 +4211,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764260</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4161,6 +4326,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764275</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4271,6 +4441,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764302</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4381,6 +4556,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764305</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4491,8 +4671,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764380</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>